--- a/treasury-bonds/annual-zeros-1961.xlsx
+++ b/treasury-bonds/annual-zeros-1961.xlsx
@@ -1,40 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansa1\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asarantsev\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F7F0774-081F-4559-B6A5-4B4304E546D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA419CE4-5EA2-4559-B72F-B113376D2441}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{6D321AAF-CF23-4C27-84B2-AF34D2EE9782}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17505" activeTab="2" xr2:uid="{6D321AAF-CF23-4C27-84B2-AF34D2EE9782}"/>
   </bookViews>
   <sheets>
     <sheet name="zeros" sheetId="1" r:id="rId1"/>
     <sheet name="summary" sheetId="2" r:id="rId2"/>
+    <sheet name="readme" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="26">
   <si>
     <t>Date</t>
   </si>
@@ -84,7 +72,34 @@
     <t>Year</t>
   </si>
   <si>
-    <t>Volatility</t>
+    <t>We take zero-coupon data for maturities 1 to 10 years</t>
+  </si>
+  <si>
+    <t>https://www.federalreserve.gov/econres/feds/the-us-treasury-yield-curve-1961-to-the-present.htm</t>
+  </si>
+  <si>
+    <t>Continuously compounded zero-coupon rates</t>
+  </si>
+  <si>
+    <t>end of year data 1961-2026</t>
+  </si>
+  <si>
+    <t>Also, we take classic coupon 10-year Treasury yields</t>
+  </si>
+  <si>
+    <t>copied from our main data library from 1927, December daily average</t>
+  </si>
+  <si>
+    <t>And compare resulting returns of 10-year zero-coupon bonds</t>
+  </si>
+  <si>
+    <t>True returns (target) and approximated returns (benchmark)</t>
+  </si>
+  <si>
+    <t>We copies the last two columns from the sheet zeros to the sheet summary</t>
+  </si>
+  <si>
+    <t>For convenience</t>
   </si>
 </sst>
 </file>
@@ -94,7 +109,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -242,6 +257,12 @@
       <name val="Cambria"/>
       <family val="1"/>
       <charset val="204"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Cambria"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="33">
@@ -602,9 +623,7 @@
     <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -981,16 +1000,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E4A4214-971B-4E7D-BAC6-F0457A6E6D4C}">
   <dimension ref="A1:N233"/>
-  <sheetFormatPr defaultRowHeight="20.25" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="20.25"/>
   <cols>
-    <col min="1" max="1" width="20.5703125" style="2" customWidth="1"/>
-    <col min="2" max="12" width="12.7109375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="20.625" style="2" customWidth="1"/>
+    <col min="2" max="12" width="12.75" style="2" customWidth="1"/>
     <col min="13" max="13" width="13" style="4" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="13" style="4" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="2"/>
+    <col min="15" max="16384" width="9.125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1034,7 +1053,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>22644</v>
       </c>
@@ -1072,7 +1091,7 @@
         <v>4.0599999999999996</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
         <v>23011</v>
       </c>
@@ -1114,7 +1133,7 @@
         <v>0.99786495458999303</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14">
       <c r="A4" s="3">
         <v>23376</v>
       </c>
@@ -1156,7 +1175,7 @@
         <v>0.99736558589664415</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14">
       <c r="A5" s="3">
         <v>23742</v>
       </c>
@@ -1198,7 +1217,7 @@
         <v>0.97702632892696006</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14">
       <c r="A6" s="3">
         <v>24107</v>
       </c>
@@ -1236,7 +1255,7 @@
         <v>4.62</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14">
       <c r="A7" s="3">
         <v>24471</v>
       </c>
@@ -1274,7 +1293,7 @@
         <v>4.84</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14">
       <c r="A8" s="3">
         <v>24835</v>
       </c>
@@ -1312,7 +1331,7 @@
         <v>5.7</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14">
       <c r="A9" s="3">
         <v>25203</v>
       </c>
@@ -1350,7 +1369,7 @@
         <v>6.03</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14">
       <c r="A10" s="3">
         <v>25568</v>
       </c>
@@ -1388,7 +1407,7 @@
         <v>7.65</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14">
       <c r="A11" s="3">
         <v>25933</v>
       </c>
@@ -1426,7 +1445,7 @@
         <v>6.39</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14">
       <c r="A12" s="3">
         <v>26298</v>
       </c>
@@ -1472,7 +1491,7 @@
         <v>2.0599999999999952E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14">
       <c r="A13" s="3">
         <v>26662</v>
       </c>
@@ -1518,7 +1537,7 @@
         <v>2.9399999999999978E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14">
       <c r="A14" s="3">
         <v>27029</v>
       </c>
@@ -1564,7 +1583,7 @@
         <v>5.3000000000000113E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14">
       <c r="A15" s="3">
         <v>27394</v>
       </c>
@@ -1610,7 +1629,7 @@
         <v>2.2999999999999972E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14">
       <c r="A16" s="3">
         <v>27759</v>
       </c>
@@ -1656,7 +1675,7 @@
         <v>0.18170000000000003</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14">
       <c r="A17" s="3">
         <v>28125</v>
       </c>
@@ -1702,7 +1721,7 @@
         <v>-5.1000000000000515E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14">
       <c r="A18" s="3">
         <v>28489</v>
       </c>
@@ -1748,7 +1767,7 @@
         <v>-4.1899999999999979E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14">
       <c r="A19" s="3">
         <v>28853</v>
       </c>
@@ -1794,7 +1813,7 @@
         <v>-3.4100000000000109E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14">
       <c r="A20" s="3">
         <v>29220</v>
       </c>
@@ -1840,7 +1859,7 @@
         <v>-0.11659999999999997</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14">
       <c r="A21" s="3">
         <v>29586</v>
       </c>
@@ -1886,7 +1905,7 @@
         <v>4.9200000000000021E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14">
       <c r="A22" s="3">
         <v>29951</v>
       </c>
@@ -1932,7 +1951,7 @@
         <v>0.42340000000000033</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14">
       <c r="A23" s="3">
         <v>30316</v>
       </c>
@@ -1978,7 +1997,7 @@
         <v>-1.0700000000000074E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14">
       <c r="A24" s="3">
         <v>30680</v>
       </c>
@@ -2024,7 +2043,7 @@
         <v>0.14799999999999996</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14">
       <c r="A25" s="3">
         <v>31047</v>
       </c>
@@ -2070,7 +2089,7 @@
         <v>0.31659999999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14">
       <c r="A26" s="3">
         <v>31412</v>
       </c>
@@ -2116,7 +2135,7 @@
         <v>0.28609999999999991</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14">
       <c r="A27" s="3">
         <v>31777</v>
       </c>
@@ -2162,7 +2181,7 @@
         <v>-9.8099999999999882E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14">
       <c r="A28" s="3">
         <v>32142</v>
       </c>
@@ -2208,7 +2227,7 @@
         <v>7.9100000000000115E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14">
       <c r="A29" s="3">
         <v>32507</v>
       </c>
@@ -2254,7 +2273,7 @@
         <v>0.20539999999999992</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14">
       <c r="A30" s="3">
         <v>32871</v>
       </c>
@@ -2300,7 +2319,7 @@
         <v>5.6800000000000073E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14">
       <c r="A31" s="3">
         <v>33238</v>
       </c>
@@ -2346,7 +2365,7 @@
         <v>0.16989999999999994</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14">
       <c r="A32" s="3">
         <v>33603</v>
       </c>
@@ -2392,7 +2411,7 @@
         <v>9.9700000000000136E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:14">
       <c r="A33" s="3">
         <v>33968</v>
       </c>
@@ -2438,7 +2457,7 @@
         <v>0.15769999999999995</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:14">
       <c r="A34" s="3">
         <v>34334</v>
       </c>
@@ -2484,7 +2503,7 @@
         <v>-0.12589999999999996</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:14">
       <c r="A35" s="3">
         <v>34698</v>
       </c>
@@ -2530,7 +2549,7 @@
         <v>0.26709999999999995</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:14">
       <c r="A36" s="3">
         <v>35062</v>
       </c>
@@ -2576,7 +2595,7 @@
         <v>4.0000000000000573E-3</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:14">
       <c r="A37" s="3">
         <v>35430</v>
       </c>
@@ -2622,7 +2641,7 @@
         <v>0.10710000000000001</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:14">
       <c r="A38" s="3">
         <v>35795</v>
       </c>
@@ -2668,7 +2687,7 @@
         <v>0.16249999999999992</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:14">
       <c r="A39" s="3">
         <v>36160</v>
       </c>
@@ -2714,7 +2733,7 @@
         <v>-0.10020000000000004</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:14">
       <c r="A40" s="3">
         <v>36525</v>
       </c>
@@ -2760,7 +2779,7 @@
         <v>0.15640000000000001</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:14">
       <c r="A41" s="3">
         <v>36889</v>
       </c>
@@ -2806,7 +2825,7 @@
         <v>6.5900000000000042E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:14">
       <c r="A42" s="3">
         <v>37256</v>
       </c>
@@ -2852,7 +2871,7 @@
         <v>0.14629999999999996</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:14">
       <c r="A43" s="3">
         <v>37621</v>
       </c>
@@ -2898,7 +2917,7 @@
         <v>1.8700000000000116E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:14">
       <c r="A44" s="3">
         <v>37986</v>
       </c>
@@ -2944,7 +2963,7 @@
         <v>4.6299999999999883E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:14">
       <c r="A45" s="3">
         <v>38352</v>
       </c>
@@ -2990,7 +3009,7 @@
         <v>2.0700000000000076E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:14">
       <c r="A46" s="3">
         <v>38716</v>
       </c>
@@ -3036,7 +3055,7 @@
         <v>3.6599999999999966E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:14">
       <c r="A47" s="3">
         <v>39080</v>
       </c>
@@ -3082,7 +3101,7 @@
         <v>8.6999999999999952E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:14">
       <c r="A48" s="3">
         <v>39447</v>
       </c>
@@ -3128,7 +3147,7 @@
         <v>0.19219999999999998</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:14">
       <c r="A49" s="3">
         <v>39813</v>
       </c>
@@ -3174,7 +3193,7 @@
         <v>-8.1100000000000033E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:14">
       <c r="A50" s="3">
         <v>40178</v>
       </c>
@@ -3220,7 +3239,7 @@
         <v>6.2899999999999998E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:14">
       <c r="A51" s="3">
         <v>40543</v>
       </c>
@@ -3266,7 +3285,7 @@
         <v>0.15079999999999999</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:14">
       <c r="A52" s="3">
         <v>40907</v>
       </c>
@@ -3312,7 +3331,7 @@
         <v>4.3200000000000002E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:14">
       <c r="A53" s="3">
         <v>41274</v>
       </c>
@@ -3358,7 +3377,7 @@
         <v>-8.8999999999999982E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:14">
       <c r="A54" s="3">
         <v>41639</v>
       </c>
@@ -3404,7 +3423,7 @@
         <v>9.11E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:14">
       <c r="A55" s="3">
         <v>42004</v>
       </c>
@@ -3450,7 +3469,7 @@
         <v>1.9399999999999976E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:14">
       <c r="A56" s="3">
         <v>42369</v>
       </c>
@@ -3496,7 +3515,7 @@
         <v>-1.0000000000001563E-4</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:14">
       <c r="A57" s="3">
         <v>42734</v>
       </c>
@@ -3542,7 +3561,7 @@
         <v>3.3000000000000043E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:14">
       <c r="A58" s="3">
         <v>43098</v>
       </c>
@@ -3588,7 +3607,7 @@
         <v>-1.4699999999999989E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:14">
       <c r="A59" s="3">
         <v>43465</v>
       </c>
@@ -3634,7 +3653,7 @@
         <v>0.11559999999999999</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:14">
       <c r="A60" s="3">
         <v>43830</v>
       </c>
@@ -3680,7 +3699,7 @@
         <v>0.1023</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:14">
       <c r="A61" s="3">
         <v>44196</v>
       </c>
@@ -3726,7 +3745,7 @@
         <v>-3.9299999999999995E-2</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:14">
       <c r="A62" s="3">
         <v>44561</v>
       </c>
@@ -3772,7 +3791,7 @@
         <v>-0.17879999999999999</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:14">
       <c r="A63" s="3">
         <v>44925</v>
       </c>
@@ -3818,7 +3837,7 @@
         <v>2.0000000000010233E-4</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:14">
       <c r="A64" s="3">
         <v>45289</v>
       </c>
@@ -3864,7 +3883,7 @@
         <v>6.8999999999999773E-3</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:14">
       <c r="A65" s="3">
         <v>45657</v>
       </c>
@@ -3910,7 +3929,7 @@
         <v>6.6400000000000001E-2</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:14">
       <c r="A66" s="3">
         <v>46022</v>
       </c>
@@ -3948,505 +3967,505 @@
         <v>4.1399999999999997</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:14">
       <c r="A67" s="3"/>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:14">
       <c r="A68" s="3"/>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:14">
       <c r="A69" s="3"/>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:14">
       <c r="A70" s="3"/>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:14">
       <c r="A71" s="3"/>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:14">
       <c r="A72" s="3"/>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:14">
       <c r="A73" s="3"/>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:14">
       <c r="A74" s="3"/>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:14">
       <c r="A75" s="3"/>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:14">
       <c r="A76" s="3"/>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:14">
       <c r="A77" s="3"/>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:14">
       <c r="A78" s="3"/>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:14">
       <c r="A79" s="3"/>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:14">
       <c r="A80" s="3"/>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:1">
       <c r="A81" s="3"/>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:1">
       <c r="A82" s="3"/>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:1">
       <c r="A83" s="3"/>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:1">
       <c r="A84" s="3"/>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:1">
       <c r="A85" s="3"/>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:1">
       <c r="A86" s="3"/>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:1">
       <c r="A87" s="3"/>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:1">
       <c r="A88" s="3"/>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:1">
       <c r="A89" s="3"/>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:1">
       <c r="A90" s="3"/>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:1">
       <c r="A91" s="3"/>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:1">
       <c r="A92" s="3"/>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:1">
       <c r="A93" s="3"/>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:1">
       <c r="A94" s="3"/>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:1">
       <c r="A95" s="3"/>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:1">
       <c r="A96" s="3"/>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:1">
       <c r="A97" s="3"/>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:1">
       <c r="A98" s="3"/>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:1">
       <c r="A99" s="3"/>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:1">
       <c r="A100" s="3"/>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:1">
       <c r="A101" s="3"/>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:1">
       <c r="A102" s="3"/>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:1">
       <c r="A103" s="3"/>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:1">
       <c r="A104" s="3"/>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:1">
       <c r="A105" s="3"/>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:1">
       <c r="A106" s="3"/>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:1">
       <c r="A107" s="3"/>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:1">
       <c r="A108" s="3"/>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:1">
       <c r="A109" s="3"/>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:1">
       <c r="A110" s="3"/>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:1">
       <c r="A111" s="3"/>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:1">
       <c r="A112" s="3"/>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:1">
       <c r="A113" s="3"/>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:1">
       <c r="A114" s="3"/>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:1">
       <c r="A115" s="3"/>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:1">
       <c r="A116" s="3"/>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:1">
       <c r="A117" s="3"/>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:1">
       <c r="A118" s="3"/>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:1">
       <c r="A119" s="3"/>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:1">
       <c r="A120" s="3"/>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:1">
       <c r="A121" s="3"/>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:1">
       <c r="A122" s="3"/>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:1">
       <c r="A123" s="3"/>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:1">
       <c r="A124" s="3"/>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:1">
       <c r="A125" s="3"/>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:1">
       <c r="A126" s="3"/>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:1">
       <c r="A127" s="3"/>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:1">
       <c r="A128" s="3"/>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:1">
       <c r="A129" s="3"/>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:1">
       <c r="A130" s="3"/>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:1">
       <c r="A131" s="3"/>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:1">
       <c r="A132" s="3"/>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:1">
       <c r="A133" s="3"/>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:1">
       <c r="A134" s="3"/>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:1">
       <c r="A135" s="3"/>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:1">
       <c r="A136" s="3"/>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:1">
       <c r="A137" s="3"/>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:1">
       <c r="A138" s="3"/>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:1">
       <c r="A139" s="3"/>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:1">
       <c r="A140" s="3"/>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:1">
       <c r="A141" s="3"/>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:1">
       <c r="A142" s="3"/>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:1">
       <c r="A143" s="3"/>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:1">
       <c r="A144" s="3"/>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:1">
       <c r="A145" s="3"/>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:1">
       <c r="A146" s="3"/>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:1">
       <c r="A147" s="3"/>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:1">
       <c r="A148" s="3"/>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:1">
       <c r="A149" s="3"/>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:1">
       <c r="A150" s="3"/>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:1">
       <c r="A151" s="3"/>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:1">
       <c r="A152" s="3"/>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:1">
       <c r="A153" s="3"/>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:1">
       <c r="A154" s="3"/>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:1">
       <c r="A155" s="3"/>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:1">
       <c r="A156" s="3"/>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:1">
       <c r="A157" s="3"/>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:1">
       <c r="A158" s="3"/>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:1">
       <c r="A159" s="3"/>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:1">
       <c r="A160" s="3"/>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:1">
       <c r="A161" s="3"/>
     </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:1">
       <c r="A162" s="3"/>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:1">
       <c r="A163" s="3"/>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:1">
       <c r="A164" s="3"/>
     </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:1">
       <c r="A165" s="3"/>
     </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:1">
       <c r="A166" s="3"/>
     </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:1">
       <c r="A167" s="3"/>
     </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:1">
       <c r="A168" s="3"/>
     </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:1">
       <c r="A169" s="3"/>
     </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:1">
       <c r="A170" s="3"/>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:1">
       <c r="A171" s="3"/>
     </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:1">
       <c r="A172" s="3"/>
     </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:1">
       <c r="A173" s="3"/>
     </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:1">
       <c r="A174" s="3"/>
     </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:1">
       <c r="A175" s="3"/>
     </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:1">
       <c r="A176" s="3"/>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:1">
       <c r="A177" s="3"/>
     </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:1">
       <c r="A178" s="3"/>
     </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:1">
       <c r="A179" s="3"/>
     </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:1">
       <c r="A180" s="3"/>
     </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:1">
       <c r="A181" s="3"/>
     </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:1">
       <c r="A182" s="3"/>
     </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:1">
       <c r="A183" s="3"/>
     </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:1">
       <c r="A184" s="3"/>
     </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:1">
       <c r="A185" s="3"/>
     </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:1">
       <c r="A186" s="3"/>
     </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:1">
       <c r="A187" s="3"/>
     </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:1">
       <c r="A188" s="3"/>
     </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:1">
       <c r="A189" s="3"/>
     </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:1">
       <c r="A190" s="3"/>
     </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:1">
       <c r="A191" s="3"/>
     </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:1">
       <c r="A192" s="3"/>
     </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:1">
       <c r="A193" s="3"/>
     </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:1">
       <c r="A194" s="3"/>
     </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:1">
       <c r="A195" s="3"/>
     </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:1">
       <c r="A196" s="3"/>
     </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:1">
       <c r="A197" s="3"/>
     </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:1">
       <c r="A198" s="3"/>
     </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:1">
       <c r="A199" s="3"/>
     </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:1">
       <c r="A200" s="3"/>
     </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:1">
       <c r="A201" s="3"/>
     </row>
-    <row r="202" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:1">
       <c r="A202" s="3"/>
     </row>
-    <row r="203" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:1">
       <c r="A203" s="3"/>
     </row>
-    <row r="204" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:1">
       <c r="A204" s="3"/>
     </row>
-    <row r="205" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:1">
       <c r="A205" s="3"/>
     </row>
-    <row r="206" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:1">
       <c r="A206" s="3"/>
     </row>
-    <row r="207" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:1">
       <c r="A207" s="3"/>
     </row>
-    <row r="208" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:1">
       <c r="A208" s="3"/>
     </row>
-    <row r="209" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:1">
       <c r="A209" s="3"/>
     </row>
-    <row r="210" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:1">
       <c r="A210" s="3"/>
     </row>
-    <row r="211" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:1">
       <c r="A211" s="3"/>
     </row>
-    <row r="212" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:1">
       <c r="A212" s="3"/>
     </row>
-    <row r="213" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:1">
       <c r="A213" s="3"/>
     </row>
-    <row r="214" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:1">
       <c r="A214" s="3"/>
     </row>
-    <row r="215" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:1">
       <c r="A215" s="3"/>
     </row>
-    <row r="216" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:1">
       <c r="A216" s="3"/>
     </row>
-    <row r="217" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:1">
       <c r="A217" s="3"/>
     </row>
-    <row r="218" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:1">
       <c r="A218" s="3"/>
     </row>
-    <row r="219" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:1">
       <c r="A219" s="3"/>
     </row>
-    <row r="220" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:1">
       <c r="A220" s="3"/>
     </row>
-    <row r="221" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:1">
       <c r="A221" s="3"/>
     </row>
-    <row r="222" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:1">
       <c r="A222" s="3"/>
     </row>
-    <row r="223" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:1">
       <c r="A223" s="3"/>
     </row>
-    <row r="224" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:1">
       <c r="A224" s="3"/>
     </row>
-    <row r="225" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:1">
       <c r="A225" s="3"/>
     </row>
-    <row r="226" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:1">
       <c r="A226" s="3"/>
     </row>
-    <row r="227" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:1">
       <c r="A227" s="3"/>
     </row>
-    <row r="228" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:1">
       <c r="A228" s="3"/>
     </row>
-    <row r="229" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:1">
       <c r="A229" s="3"/>
     </row>
-    <row r="230" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:1">
       <c r="A230" s="3"/>
     </row>
-    <row r="231" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:1">
       <c r="A231" s="3"/>
     </row>
-    <row r="232" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:1">
       <c r="A232" s="3"/>
     </row>
-    <row r="233" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:1">
       <c r="A233" s="3"/>
     </row>
   </sheetData>
@@ -4456,15 +4475,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DE36C73-ADD0-418F-8AF3-92F09105BDDB}">
-  <dimension ref="A1:D55"/>
-  <sheetFormatPr defaultRowHeight="20.25" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C55"/>
+  <sheetFormatPr defaultRowHeight="20.25"/>
   <cols>
-    <col min="1" max="1" width="16.7109375" style="2" customWidth="1"/>
-    <col min="2" max="3" width="16.7109375" style="5" customWidth="1"/>
-    <col min="4" max="4" width="16.7109375" customWidth="1"/>
+    <col min="1" max="1" width="16.75" style="2" customWidth="1"/>
+    <col min="2" max="3" width="16.75" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="2" t="s">
         <v>15</v>
       </c>
@@ -4474,767 +4492,774 @@
       <c r="C1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" s="2">
         <v>1972</v>
       </c>
       <c r="B2" s="5">
+        <f>zeros!M12</f>
         <v>3.2901999999999987E-2</v>
       </c>
       <c r="C2" s="5">
+        <f>zeros!N12</f>
         <v>2.0599999999999952E-2</v>
       </c>
-      <c r="D2" s="6">
-        <v>5.0126840000000001</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" s="2">
         <v>1973</v>
       </c>
       <c r="B3" s="5">
+        <f>zeros!M13</f>
         <v>2.1972000000000023E-2</v>
       </c>
       <c r="C3" s="5">
+        <f>zeros!N13</f>
         <v>2.9399999999999978E-2</v>
       </c>
-      <c r="D3" s="6">
-        <v>9.9676930000000006</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" s="2">
         <v>1974</v>
       </c>
       <c r="B4" s="5">
+        <f>zeros!M14</f>
         <v>2.9235000000000042E-2</v>
       </c>
       <c r="C4" s="5">
+        <f>zeros!N14</f>
         <v>5.3000000000000113E-3</v>
       </c>
-      <c r="D4" s="6">
-        <v>13.716265</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" s="2">
         <v>1975</v>
       </c>
       <c r="B5" s="5">
+        <f>zeros!M15</f>
         <v>3.0765999999999991E-2</v>
       </c>
       <c r="C5" s="5">
+        <f>zeros!N15</f>
         <v>2.2999999999999972E-2</v>
       </c>
-      <c r="D5" s="6">
-        <v>9.7030209999999997</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" s="2">
         <v>1976</v>
       </c>
       <c r="B6" s="5">
+        <f>zeros!M16</f>
         <v>0.16465399999999997</v>
       </c>
       <c r="C6" s="5">
+        <f>zeros!N16</f>
         <v>0.18170000000000003</v>
       </c>
-      <c r="D6" s="6">
-        <v>6.9896979999999997</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7" s="2">
         <v>1977</v>
       </c>
       <c r="B7" s="5">
+        <f>zeros!M17</f>
         <v>-1.57350000000001E-2</v>
       </c>
       <c r="C7" s="5">
+        <f>zeros!N17</f>
         <v>-5.1000000000000515E-3</v>
       </c>
-      <c r="D7" s="6">
-        <v>5.7213389999999995</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:3">
       <c r="A8" s="2">
         <v>1978</v>
       </c>
       <c r="B8" s="5">
+        <f>zeros!M18</f>
         <v>-2.5716999999999785E-2</v>
       </c>
       <c r="C8" s="5">
+        <f>zeros!N18</f>
         <v>-4.1899999999999979E-2</v>
       </c>
-      <c r="D8" s="6">
-        <v>7.9206069999999995</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:3">
       <c r="A9" s="2">
         <v>1979</v>
       </c>
       <c r="B9" s="5">
+        <f>zeros!M19</f>
         <v>-1.4926000000000102E-2</v>
       </c>
       <c r="C9" s="5">
+        <f>zeros!N19</f>
         <v>-3.4100000000000109E-2</v>
       </c>
-      <c r="D9" s="6">
-        <v>6.8351510000000006</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:3">
       <c r="A10" s="2">
         <v>1980</v>
       </c>
       <c r="B10" s="5">
+        <f>zeros!M20</f>
         <v>-7.1294999999999928E-2</v>
       </c>
       <c r="C10" s="5">
+        <f>zeros!N20</f>
         <v>-0.11659999999999997</v>
       </c>
-      <c r="D10" s="6">
-        <v>10.373337999999999</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:3">
       <c r="A11" s="2">
         <v>1981</v>
       </c>
       <c r="B11" s="5">
+        <f>zeros!M21</f>
         <v>-3.1624999999999945E-2</v>
       </c>
       <c r="C11" s="5">
+        <f>zeros!N21</f>
         <v>4.9200000000000021E-2</v>
       </c>
-      <c r="D11" s="6">
-        <v>8.4787419999999987</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:3">
       <c r="A12" s="2">
         <v>1982</v>
       </c>
       <c r="B12" s="5">
+        <f>zeros!M22</f>
         <v>0.40761399999999998</v>
       </c>
       <c r="C12" s="5">
+        <f>zeros!N22</f>
         <v>0.42340000000000033</v>
       </c>
-      <c r="D12" s="6">
-        <v>11.454578999999999</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:3">
       <c r="A13" s="2">
         <v>1983</v>
       </c>
       <c r="B13" s="5">
+        <f>zeros!M23</f>
         <v>3.3759999999999481E-3</v>
       </c>
       <c r="C13" s="5">
+        <f>zeros!N23</f>
         <v>-1.0700000000000074E-2</v>
       </c>
-      <c r="D13" s="6">
-        <v>8.386317</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:3">
       <c r="A14" s="2">
         <v>1984</v>
       </c>
       <c r="B14" s="5">
+        <f>zeros!M24</f>
         <v>0.13510999999999995</v>
       </c>
       <c r="C14" s="5">
+        <f>zeros!N24</f>
         <v>0.14799999999999996</v>
       </c>
-      <c r="D14" s="6">
-        <v>8.0041060000000002</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:3">
       <c r="A15" s="2">
         <v>1985</v>
       </c>
       <c r="B15" s="5">
+        <f>zeros!M25</f>
         <v>0.33028799999999991</v>
       </c>
       <c r="C15" s="5">
+        <f>zeros!N25</f>
         <v>0.31659999999999999</v>
       </c>
-      <c r="D15" s="6">
-        <v>6.3878360000000001</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:3">
       <c r="A16" s="2">
         <v>1986</v>
       </c>
       <c r="B16" s="5">
+        <f>zeros!M26</f>
         <v>0.24701499999999982</v>
       </c>
       <c r="C16" s="5">
+        <f>zeros!N26</f>
         <v>0.28609999999999991</v>
       </c>
-      <c r="D16" s="6">
-        <v>9.2917199999999998</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17" s="2">
         <v>1987</v>
       </c>
       <c r="B17" s="5">
+        <f>zeros!M27</f>
         <v>-4.2689785265990141E-2</v>
       </c>
       <c r="C17" s="5">
+        <f>zeros!N27</f>
         <v>-9.8099999999999882E-2</v>
       </c>
-      <c r="D17" s="6">
-        <v>21.250115999999998</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18" s="2">
         <v>1988</v>
       </c>
       <c r="B18" s="5">
+        <f>zeros!M28</f>
         <v>8.3190382887379857E-2</v>
       </c>
       <c r="C18" s="5">
+        <f>zeros!N28</f>
         <v>7.9100000000000115E-2</v>
       </c>
-      <c r="D18" s="6">
-        <v>10.815429</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19" s="2">
         <v>1989</v>
       </c>
       <c r="B19" s="5">
+        <f>zeros!M29</f>
         <v>0.18943865445716002</v>
       </c>
       <c r="C19" s="5">
+        <f>zeros!N29</f>
         <v>0.20539999999999992</v>
       </c>
-      <c r="D19" s="6">
-        <v>8.2773800000000008</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:3">
       <c r="A20" s="2">
         <v>1990</v>
       </c>
       <c r="B20" s="5">
+        <f>zeros!M30</f>
         <v>5.7996206564990022E-2</v>
       </c>
       <c r="C20" s="5">
+        <f>zeros!N30</f>
         <v>5.6800000000000073E-2</v>
       </c>
-      <c r="D20" s="6">
-        <v>10.057228</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:3">
       <c r="A21" s="2">
         <v>1991</v>
       </c>
       <c r="B21" s="5">
+        <f>zeros!M31</f>
         <v>0.19295278178948003</v>
       </c>
       <c r="C21" s="5">
+        <f>zeros!N31</f>
         <v>0.16989999999999994</v>
       </c>
-      <c r="D21" s="6">
-        <v>8.9910430000000012</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:3">
       <c r="A22" s="2">
         <v>1992</v>
       </c>
       <c r="B22" s="5">
+        <f>zeros!M32</f>
         <v>8.4474265135490043E-2</v>
       </c>
       <c r="C22" s="5">
+        <f>zeros!N32</f>
         <v>9.9700000000000136E-2</v>
       </c>
-      <c r="D22" s="6">
-        <v>6.0971729999999997</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:3">
       <c r="A23" s="2">
         <v>1993</v>
       </c>
       <c r="B23" s="5">
+        <f>zeros!M33</f>
         <v>0.17436653089330009</v>
       </c>
       <c r="C23" s="5">
+        <f>zeros!N33</f>
         <v>0.15769999999999995</v>
       </c>
-      <c r="D23" s="6">
-        <v>5.4191520000000004</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:3">
       <c r="A24" s="2">
         <v>1994</v>
       </c>
       <c r="B24" s="5">
+        <f>zeros!M34</f>
         <v>-9.4894672241499903E-2</v>
       </c>
       <c r="C24" s="5">
+        <f>zeros!N34</f>
         <v>-0.12589999999999996</v>
       </c>
-      <c r="D24" s="6">
-        <v>6.2068820000000002</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:3">
       <c r="A25" s="2">
         <v>1995</v>
       </c>
       <c r="B25" s="5">
+        <f>zeros!M35</f>
         <v>0.27503892471199998</v>
       </c>
       <c r="C25" s="5">
+        <f>zeros!N35</f>
         <v>0.26709999999999995</v>
       </c>
-      <c r="D25" s="6">
-        <v>4.9127040000000006</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:3">
       <c r="A26" s="2">
         <v>1996</v>
       </c>
       <c r="B26" s="5">
+        <f>zeros!M36</f>
         <v>-6.2494344062900354E-3</v>
       </c>
       <c r="C26" s="5">
+        <f>zeros!N36</f>
         <v>4.0000000000000573E-3</v>
       </c>
-      <c r="D26" s="6">
-        <v>7.4320130000000004</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:3">
       <c r="A27" s="2">
         <v>1997</v>
       </c>
       <c r="B27" s="5">
+        <f>zeros!M37</f>
         <v>0.12634535799448998</v>
       </c>
       <c r="C27" s="5">
+        <f>zeros!N37</f>
         <v>0.10710000000000001</v>
       </c>
-      <c r="D27" s="6">
-        <v>11.449778</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:3">
       <c r="A28" s="2">
         <v>1998</v>
       </c>
       <c r="B28" s="5">
+        <f>zeros!M38</f>
         <v>0.13436533626279995</v>
       </c>
       <c r="C28" s="5">
+        <f>zeros!N38</f>
         <v>0.16249999999999992</v>
       </c>
-      <c r="D28" s="6">
-        <v>12.814732000000001</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:3">
       <c r="A29" s="2">
         <v>1999</v>
       </c>
       <c r="B29" s="5">
+        <f>zeros!M39</f>
         <v>-9.8274321447640034E-2</v>
       </c>
       <c r="C29" s="5">
+        <f>zeros!N39</f>
         <v>-0.10020000000000004</v>
       </c>
-      <c r="D29" s="6">
-        <v>11.370733</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:3">
       <c r="A30" s="2">
         <v>2000</v>
       </c>
       <c r="B30" s="5">
+        <f>zeros!M40</f>
         <v>0.19447117287620003</v>
       </c>
       <c r="C30" s="5">
+        <f>zeros!N40</f>
         <v>0.15640000000000001</v>
       </c>
-      <c r="D30" s="6">
-        <v>14.001749999999999</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:3">
       <c r="A31" s="2">
         <v>2001</v>
       </c>
       <c r="B31" s="5">
+        <f>zeros!M41</f>
         <v>4.96252076815E-2</v>
       </c>
       <c r="C31" s="5">
+        <f>zeros!N41</f>
         <v>6.5900000000000042E-2</v>
       </c>
-      <c r="D31" s="6">
-        <v>13.582177000000001</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:3">
       <c r="A32" s="2">
         <v>2002</v>
       </c>
       <c r="B32" s="5">
+        <f>zeros!M42</f>
         <v>0.18820700000000001</v>
       </c>
       <c r="C32" s="5">
+        <f>zeros!N42</f>
         <v>0.14629999999999996</v>
       </c>
-      <c r="D32" s="6">
-        <v>16.353704999999998</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:3">
       <c r="A33" s="2">
         <v>2003</v>
       </c>
       <c r="B33" s="5">
+        <f>zeros!M43</f>
         <v>3.2533000000000027E-2</v>
       </c>
       <c r="C33" s="5">
+        <f>zeros!N43</f>
         <v>1.8700000000000116E-2</v>
       </c>
-      <c r="D33" s="6">
-        <v>10.737346000000001</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:3">
       <c r="A34" s="2">
         <v>2004</v>
       </c>
       <c r="B34" s="5">
+        <f>zeros!M44</f>
         <v>7.1194000000000063E-2</v>
       </c>
       <c r="C34" s="5">
+        <f>zeros!N44</f>
         <v>4.6299999999999883E-2</v>
       </c>
-      <c r="D34" s="6">
-        <v>6.9883180000000005</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:3">
       <c r="A35" s="2">
         <v>2005</v>
       </c>
       <c r="B35" s="5">
+        <f>zeros!M45</f>
         <v>4.4664000000000002E-2</v>
       </c>
       <c r="C35" s="5">
+        <f>zeros!N45</f>
         <v>2.0700000000000076E-2</v>
       </c>
-      <c r="D35" s="6">
-        <v>6.4773430000000003</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="1:3">
       <c r="A36" s="2">
         <v>2006</v>
       </c>
       <c r="B36" s="5">
+        <f>zeros!M46</f>
         <v>2.0716000000000036E-2</v>
       </c>
       <c r="C36" s="5">
+        <f>zeros!N46</f>
         <v>3.6599999999999966E-2</v>
       </c>
-      <c r="D36" s="6">
-        <v>6.3097780000000006</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="37" spans="1:3">
       <c r="A37" s="2">
         <v>2007</v>
       </c>
       <c r="B37" s="5">
+        <f>zeros!M47</f>
         <v>9.9643999999999983E-2</v>
       </c>
       <c r="C37" s="5">
+        <f>zeros!N47</f>
         <v>8.6999999999999952E-2</v>
       </c>
-      <c r="D37" s="6">
-        <v>10.092566000000001</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="38" spans="1:3">
       <c r="A38" s="2">
         <v>2008</v>
       </c>
       <c r="B38" s="5">
+        <f>zeros!M48</f>
         <v>0.18616600545883205</v>
       </c>
       <c r="C38" s="5">
+        <f>zeros!N48</f>
         <v>0.19219999999999998</v>
       </c>
-      <c r="D38" s="6">
-        <v>25.840084999999998</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="39" spans="1:3">
       <c r="A39" s="2">
         <v>2009</v>
       </c>
       <c r="B39" s="5">
+        <f>zeros!M49</f>
         <v>-7.0074000358581509E-2</v>
       </c>
       <c r="C39" s="5">
+        <f>zeros!N49</f>
         <v>-8.1100000000000033E-2</v>
       </c>
-      <c r="D39" s="6">
-        <v>17.175947999999998</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="40" spans="1:3">
       <c r="A40" s="2">
         <v>2010</v>
       </c>
       <c r="B40" s="5">
+        <f>zeros!M50</f>
         <v>0.11872902870178237</v>
       </c>
       <c r="C40" s="5">
+        <f>zeros!N50</f>
         <v>6.2899999999999998E-2</v>
       </c>
-      <c r="D40" s="6">
-        <v>11.377806000000001</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="41" spans="1:3">
       <c r="A41" s="2">
         <v>2011</v>
       </c>
       <c r="B41" s="5">
+        <f>zeros!M51</f>
         <v>0.19281299948692301</v>
       </c>
       <c r="C41" s="5">
+        <f>zeros!N51</f>
         <v>0.15079999999999999</v>
       </c>
-      <c r="D41" s="6">
-        <v>14.711848</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="42" spans="1:3">
       <c r="A42" s="2">
         <v>2012</v>
       </c>
       <c r="B42" s="5">
+        <f>zeros!M52</f>
         <v>5.2783005237578888E-2</v>
       </c>
       <c r="C42" s="5">
+        <f>zeros!N52</f>
         <v>4.3200000000000002E-2</v>
       </c>
-      <c r="D42" s="6">
-        <v>8.0368190000000013</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="43" spans="1:3">
       <c r="A43" s="2">
         <v>2013</v>
       </c>
       <c r="B43" s="5">
+        <f>zeros!M53</f>
         <v>-9.0330996513366596E-2</v>
       </c>
       <c r="C43" s="5">
+        <f>zeros!N53</f>
         <v>-8.8999999999999982E-2</v>
       </c>
-      <c r="D43" s="6">
-        <v>6.9739969999999998</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="44" spans="1:3">
       <c r="A44" s="2">
         <v>2014</v>
       </c>
       <c r="B44" s="5">
+        <f>zeros!M54</f>
         <v>0.12481500148773129</v>
       </c>
       <c r="C44" s="5">
+        <f>zeros!N54</f>
         <v>9.11E-2</v>
       </c>
-      <c r="D44" s="6">
-        <v>7.1702459999999997</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="45" spans="1:3">
       <c r="A45" s="2">
         <v>2015</v>
       </c>
       <c r="B45" s="5">
+        <f>zeros!M55</f>
         <v>1.7140002250670711E-2</v>
       </c>
       <c r="C45" s="5">
+        <f>zeros!N55</f>
         <v>1.9399999999999976E-2</v>
       </c>
-      <c r="D45" s="6">
-        <v>9.7698769999999993</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="46" spans="1:3">
       <c r="A46" s="2">
         <v>2016</v>
       </c>
       <c r="B46" s="5">
+        <f>zeros!M56</f>
         <v>1.4730012416839956E-2</v>
       </c>
       <c r="C46" s="5">
+        <f>zeros!N56</f>
         <v>-1.0000000000001563E-4</v>
       </c>
-      <c r="D46" s="6">
-        <v>8.2598510000000012</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="47" spans="1:3">
       <c r="A47" s="2">
         <v>2017</v>
       </c>
       <c r="B47" s="5">
+        <f>zeros!M57</f>
         <v>3.85520052909855E-2</v>
       </c>
       <c r="C47" s="5">
+        <f>zeros!N57</f>
         <v>3.3000000000000043E-2</v>
       </c>
-      <c r="D47" s="6">
-        <v>4.2126320000000002</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="48" spans="1:3">
       <c r="A48" s="2">
         <v>2018</v>
       </c>
       <c r="B48" s="5">
+        <f>zeros!M58</f>
         <v>3.3589863777168105E-3</v>
       </c>
       <c r="C48" s="5">
+        <f>zeros!N58</f>
         <v>-1.4699999999999989E-2</v>
       </c>
-      <c r="D48" s="6">
-        <v>10.771202000000001</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="49" spans="1:3">
       <c r="A49" s="2">
         <v>2019</v>
       </c>
       <c r="B49" s="5">
+        <f>zeros!M59</f>
         <v>9.7605001926422519E-2</v>
       </c>
       <c r="C49" s="5">
+        <f>zeros!N59</f>
         <v>0.11559999999999999</v>
       </c>
-      <c r="D49" s="6">
-        <v>7.867661</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="50" spans="1:3">
       <c r="A50" s="2">
         <v>2020</v>
       </c>
       <c r="B50" s="5">
+        <f>zeros!M60</f>
         <v>0.120527998226166</v>
       </c>
       <c r="C50" s="5">
+        <f>zeros!N60</f>
         <v>0.1023</v>
       </c>
-      <c r="D50" s="6">
-        <v>21.850808000000001</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="51" spans="1:3">
       <c r="A51" s="2">
         <v>2021</v>
       </c>
       <c r="B51" s="5">
+        <f>zeros!M61</f>
         <v>-4.5739999999999996E-2</v>
       </c>
       <c r="C51" s="5">
+        <f>zeros!N61</f>
         <v>-3.9299999999999995E-2</v>
       </c>
-      <c r="D51" s="6">
-        <v>8.256513</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="52" spans="1:3">
       <c r="A52" s="2">
         <v>2022</v>
       </c>
       <c r="B52" s="5">
+        <f>zeros!M62</f>
         <v>-0.188222</v>
       </c>
       <c r="C52" s="5">
+        <f>zeros!N62</f>
         <v>-0.17879999999999999</v>
       </c>
-      <c r="D52" s="6">
-        <v>15.239018</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="53" spans="1:3">
       <c r="A53" s="2">
         <v>2023</v>
       </c>
       <c r="B53" s="5">
+        <f>zeros!M63</f>
         <v>3.796099999999996E-2</v>
       </c>
       <c r="C53" s="5">
+        <f>zeros!N63</f>
         <v>2.0000000000010233E-4</v>
       </c>
-      <c r="D53" s="6">
-        <v>8.2412109999999998</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="54" spans="1:3">
       <c r="A54" s="2">
         <v>2024</v>
       </c>
       <c r="B54" s="5">
+        <f>zeros!M64</f>
         <v>-1.8282000000000024E-2</v>
       </c>
       <c r="C54" s="5">
+        <f>zeros!N64</f>
         <v>6.8999999999999773E-3</v>
       </c>
-      <c r="D54" s="6">
-        <v>7.9843289999999998</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="55" spans="1:3">
       <c r="A55" s="2">
         <v>2025</v>
       </c>
       <c r="B55" s="5">
+        <f>zeros!M65</f>
         <v>8.5199999999999956E-2</v>
       </c>
       <c r="C55" s="5">
+        <f>zeros!N65</f>
         <v>6.6400000000000001E-2</v>
-      </c>
-      <c r="D55" s="6">
-        <v>11.768746</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB14C8C3-A8F6-415C-AA3C-D6814AB2CE80}">
+  <dimension ref="A1:A10"/>
+  <sheetFormatPr defaultRowHeight="20.25"/>
+  <cols>
+    <col min="1" max="16384" width="9" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>